--- a/r5-ELGA-MOPED-main/ValueSet-moped-related-person-relationship-type.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-related-person-relationship-type.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T10:07:52+00:00</t>
+    <t>2025-02-10T08:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-related-person-relationship-type.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-related-person-relationship-type.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T08:30:06+00:00</t>
+    <t>2025-02-10T08:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-related-person-relationship-type.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-related-person-relationship-type.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T08:38:31+00:00</t>
+    <t>2025-02-11T11:17:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-related-person-relationship-type.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-related-person-relationship-type.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T11:17:52+00:00</t>
+    <t>2025-02-11T16:50:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-related-person-relationship-type.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-related-person-relationship-type.xlsx
@@ -37,7 +37,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>MOPEDRelatedPersonRelationshipType</t>
+    <t>MopedRelatedPersonRelationshipType</t>
   </si>
   <si>
     <t>Title</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T16:50:04+00:00</t>
+    <t>2025-02-13T14:21:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
